--- a/Plot/exposures_meta_analysis_ovarian_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_dietary.xlsx
@@ -537,12 +537,12 @@
       <c r="E2" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
       <c r="H2" s="5" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="n"/>
       <c r="J2" s="3" t="n">
         <v>1906</v>
       </c>
@@ -568,12 +568,12 @@
       <c r="E3" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
       <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="n"/>
       <c r="J3" s="3" t="n">
         <v>73909</v>
       </c>
@@ -599,12 +599,12 @@
       <c r="E4" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="n"/>
       <c r="J4" s="3" t="n">
         <v>4611</v>
       </c>
@@ -630,12 +630,12 @@
       <c r="E5" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n">
         <v>86.7</v>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="n"/>
       <c r="J5" s="3" t="n">
         <v>63479</v>
       </c>
@@ -671,7 +671,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.0232471382484167</v>
+        <v>0.02324713824841671</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>523871</v>
@@ -698,12 +698,12 @@
       <c r="E7" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
       <c r="H7" s="5" t="n">
         <v>27.8</v>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="n"/>
       <c r="J7" s="3" t="n">
         <v>1633</v>
       </c>
@@ -718,108 +718,108 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.57</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.82</v>
+        <v>2.32</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1549127808728178</v>
+        <v>0.3169600684392591</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>41576</v>
+        <v>36513</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>4134</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.88</v>
+        <v>3.33</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>87.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.01413592378341302</v>
+        <v>0.06371753035051776</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>591029</v>
+        <v>529715</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>4497</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.33</v>
+        <v>1.88</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>88.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.06371753035051778</v>
+        <v>0.01413592378341303</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>529715</v>
+        <v>591029</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>3624</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="11">
@@ -840,12 +840,12 @@
       <c r="E11" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n"/>
       <c r="J11" s="3" t="n">
         <v>1000</v>
       </c>
@@ -871,12 +871,12 @@
       <c r="E12" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n"/>
       <c r="J12" s="3" t="n">
         <v>3442</v>
       </c>
@@ -912,7 +912,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4980193314692444</v>
+        <v>0.4980193314692448</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>583089</v>
@@ -949,7 +949,7 @@
         <v>69.3</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.007405482745728637</v>
+        <v>0.00740548274572863</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>611872</v>
@@ -961,106 +961,106 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>0.58</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>90.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.9601614254203765</v>
+        <v>0.1398697856494959</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>307213</v>
+        <v>723200</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>4002</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>omega-6_fatty_acids</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
+        <v>1.07</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>2.37</v>
+      </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr"/>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.9601614254203767</v>
+      </c>
       <c r="J16" s="3" t="n">
-        <v>6630</v>
+        <v>307213</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3238</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>omega-6_fatty_acids</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C17" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="D17" s="4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
       <c r="H17" s="5" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0.4473296420997004</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="n"/>
       <c r="J17" s="3" t="n">
-        <v>739242</v>
+        <v>6630</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>10599</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="18">
@@ -1081,12 +1081,12 @@
       <c r="E18" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
       <c r="H18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="n"/>
       <c r="J18" s="3" t="n">
         <v>82948</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.315047002652501</v>
+        <v>0.3150470026525011</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>819111</v>
@@ -1159,7 +1159,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.854887127293174</v>
+        <v>0.8548871272931741</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>336054</v>
@@ -1196,7 +1196,7 @@
         <v>57.3</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4784202102804354</v>
+        <v>0.4784202102804352</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1588466</v>
@@ -1223,12 +1223,12 @@
       <c r="E22" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="n"/>
       <c r="J22" s="3" t="n">
         <v>159957</v>
       </c>
@@ -1254,12 +1254,12 @@
       <c r="E23" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="n"/>
       <c r="J23" s="3" t="n">
         <v>521911</v>
       </c>
@@ -1274,34 +1274,34 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0.87</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>86.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.520477629217017</v>
+        <v>0.670221817796779</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>737543</v>
+        <v>896626</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>6692</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="25">
@@ -1322,12 +1322,12 @@
       <c r="E25" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="n"/>
       <c r="J25" s="3" t="n">
         <v>0</v>
       </c>
@@ -1353,12 +1353,12 @@
       <c r="E26" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="n"/>
       <c r="J26" s="3" t="n">
         <v>1014</v>
       </c>
@@ -1384,12 +1384,12 @@
       <c r="E27" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="n"/>
       <c r="J27" s="3" t="n">
         <v>2108</v>
       </c>

--- a/Plot/exposures_meta_analysis_ovarian_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_dietary.xlsx
@@ -671,7 +671,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.02324713824841671</v>
+        <v>0.0232471382484167</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>523871</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.3169600684392591</v>
+        <v>0.3169600684392594</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>36513</v>
@@ -776,7 +776,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.06371753035051776</v>
+        <v>0.06371753035051778</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>529715</v>
@@ -813,7 +813,7 @@
         <v>87.2</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01413592378341303</v>
+        <v>0.01413592378341302</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>591029</v>
@@ -912,7 +912,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4980193314692448</v>
+        <v>0.4980193314692444</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>583089</v>
@@ -949,7 +949,7 @@
         <v>69.3</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.00740548274572863</v>
+        <v>0.007405482745728637</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>611872</v>
@@ -986,7 +986,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.1398697856494959</v>
+        <v>0.1398697856494957</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>723200</v>
@@ -1023,7 +1023,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.9601614254203767</v>
+        <v>0.9601614254203765</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>307213</v>
@@ -1122,7 +1122,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.3150470026525011</v>
+        <v>0.315047002652501</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>819111</v>
@@ -1159,7 +1159,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.8548871272931741</v>
+        <v>0.854887127293174</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>336054</v>
@@ -1196,7 +1196,7 @@
         <v>57.3</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4784202102804352</v>
+        <v>0.4784202102804354</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1588466</v>
@@ -1295,7 +1295,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.670221817796779</v>
+        <v>0.6702218177967789</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>896626</v>

--- a/Plot/exposures_meta_analysis_ovarian_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_dietary.xlsx
@@ -529,18 +529,18 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="3" t="n">
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0.98</v>
@@ -591,13 +591,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
@@ -622,18 +622,18 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n">
-        <v>86.7</v>
+        <v>88.2</v>
       </c>
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="3" t="n">
@@ -646,69 +646,69 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>selenium</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>4.94</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
       <c r="H6" s="5" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.0232471382484167</v>
-      </c>
+        <v>28.4</v>
+      </c>
+      <c r="I6" s="6" t="n"/>
       <c r="J6" s="3" t="n">
-        <v>523871</v>
+        <v>1633</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>2791</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>selenium</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+        <v>0.99</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>5.9</v>
+      </c>
       <c r="H7" s="5" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="I7" s="6" t="n"/>
+        <v>86.7</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.02483136601905617</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>1633</v>
+        <v>523871</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>611</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="8">
@@ -721,25 +721,25 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.3169600684392594</v>
+        <v>0.3699680712564313</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>36513</v>
@@ -758,25 +758,25 @@
         <v>4</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.98</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.33</v>
+        <v>3.83</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>88.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.06371753035051778</v>
+        <v>0.06078493414255114</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>529715</v>
@@ -795,25 +795,25 @@
         <v>6</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>87.2</v>
+        <v>87.8</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01413592378341302</v>
+        <v>0.0130472561502979</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>591029</v>
@@ -832,13 +832,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
@@ -863,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
@@ -894,10 +894,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>1.29</v>
@@ -906,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>945.6900000000001</v>
+        <v>1353.96</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>91.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4980193314692444</v>
+        <v>0.4971204258671445</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>583089</v>
@@ -931,25 +931,25 @@
         <v>8</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>69.3</v>
+        <v>71.3</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.007405482745728637</v>
+        <v>0.006737992167500233</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>611872</v>
@@ -968,25 +968,25 @@
         <v>8</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.1398697856494957</v>
+        <v>0.1368143494983235</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>723200</v>
@@ -1005,25 +1005,25 @@
         <v>8</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.9601614254203765</v>
+        <v>0.6980065255140948</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>307213</v>
@@ -1042,13 +1042,13 @@
         <v>2</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
@@ -1073,13 +1073,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
@@ -1104,25 +1104,25 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>1.11</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.315047002652501</v>
+        <v>0.2900993420176399</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>819111</v>
@@ -1141,25 +1141,25 @@
         <v>11</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.854887127293174</v>
+        <v>0.8424433015631739</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>336054</v>
@@ -1187,16 +1187,16 @@
         <v>1.09</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>57.3</v>
+        <v>57.6</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4784202102804354</v>
+        <v>0.4623089467253695</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1588466</v>
@@ -1280,22 +1280,22 @@
         <v>1.08</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.6702218177967789</v>
+        <v>0.7089254682310198</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>896626</v>
@@ -1314,13 +1314,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
@@ -1376,13 +1376,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>

--- a/Plot/exposures_meta_analysis_ovarian_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_dietary.xlsx
@@ -702,7 +702,7 @@
         <v>86.7</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.02483136601905617</v>
+        <v>0.02483136601905619</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>523871</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.3699680712564313</v>
+        <v>0.3699680712564322</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>36513</v>
@@ -776,7 +776,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.06078493414255114</v>
+        <v>0.06078493414255117</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>529715</v>
@@ -813,7 +813,7 @@
         <v>87.8</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0130472561502979</v>
+        <v>0.01304725615029791</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>591029</v>
@@ -912,7 +912,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4971204258671445</v>
+        <v>0.497120425867145</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>583089</v>
@@ -949,7 +949,7 @@
         <v>71.3</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.006737992167500233</v>
+        <v>0.006737992167500238</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>611872</v>
@@ -986,7 +986,7 @@
         <v>77.7</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.1368143494983235</v>
+        <v>0.1368143494983236</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>723200</v>
@@ -1023,7 +1023,7 @@
         <v>90</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6980065255140948</v>
+        <v>0.6980065255140946</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>307213</v>
@@ -1122,7 +1122,7 @@
         <v>77.7</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.2900993420176399</v>
+        <v>0.2900993420176401</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>819111</v>
@@ -1159,7 +1159,7 @@
         <v>71.09999999999999</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.8424433015631739</v>
+        <v>0.8424433015631738</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>336054</v>
@@ -1196,7 +1196,7 @@
         <v>57.6</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4623089467253695</v>
+        <v>0.4623089467253692</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1588466</v>
@@ -1295,7 +1295,7 @@
         <v>84.3</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.7089254682310198</v>
+        <v>0.70892546823102</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>896626</v>
